--- a/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_CPL-DALI_LOAD_DigitalLED(V0.1).xlsx
+++ b/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_CPL-DALI_LOAD_DigitalLED(V0.1).xlsx
@@ -270,163 +270,163 @@
     <t>4.87</t>
   </si>
   <si>
+    <t>FFC 0.5mm 10Pin 90°</t>
+  </si>
+  <si>
+    <t>TE_1-1734592-0</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>-9</t>
+  </si>
+  <si>
+    <t>11.75</t>
+  </si>
+  <si>
+    <t>NLCV32T-100K-PF (10uH)</t>
+  </si>
+  <si>
+    <t>L1210</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>30.75</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>KF142R-5.08-4P</t>
+  </si>
+  <si>
+    <t>CONN-TH_4P-P5.08_KF142R-5.08-4P</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>-32.315</t>
+  </si>
+  <si>
+    <t>10.723</t>
+  </si>
+  <si>
+    <t>KF2EDGR-3.81-3Pin</t>
+  </si>
+  <si>
+    <t>CONN-TH_3P-P3.81_KF2EDGR-3.81-3P</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>-16.825</t>
+  </si>
+  <si>
+    <t>11.5</t>
+  </si>
+  <si>
+    <t>4 Pin male</t>
+  </si>
+  <si>
+    <t>TE_826647-4</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>AO3400A</t>
+  </si>
+  <si>
+    <t>SOT23 Normal</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>8.75</t>
+  </si>
+  <si>
+    <t>51k</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>-1.549</t>
+  </si>
+  <si>
+    <t>13.31</t>
+  </si>
+  <si>
+    <t>15k</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>-2.25</t>
+  </si>
+  <si>
+    <t>10.75</t>
+  </si>
+  <si>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>0402</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>-29.515</t>
+  </si>
+  <si>
+    <t>16.408</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>8.25</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
     <t>Not Fitted</t>
-  </si>
-  <si>
-    <t>FFC 0.5mm 10Pin 90°</t>
-  </si>
-  <si>
-    <t>TE_1-1734592-0</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>-9</t>
-  </si>
-  <si>
-    <t>11.75</t>
-  </si>
-  <si>
-    <t>NLCV32T-100K-PF (10uH)</t>
-  </si>
-  <si>
-    <t>L1210</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>30.75</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>KF142R-5.08-4P</t>
-  </si>
-  <si>
-    <t>CONN-TH_4P-P5.08_KF142R-5.08-4P</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>-32.315</t>
-  </si>
-  <si>
-    <t>10.723</t>
-  </si>
-  <si>
-    <t>KF2EDGR-3.81-3Pin</t>
-  </si>
-  <si>
-    <t>CONN-TH_3P-P3.81_KF2EDGR-3.81-3P</t>
-  </si>
-  <si>
-    <t>P7</t>
-  </si>
-  <si>
-    <t>-16.825</t>
-  </si>
-  <si>
-    <t>11.5</t>
-  </si>
-  <si>
-    <t>4 Pin male</t>
-  </si>
-  <si>
-    <t>TE_826647-4</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>AO3400A</t>
-  </si>
-  <si>
-    <t>SOT23 Normal</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>8.75</t>
-  </si>
-  <si>
-    <t>51k</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>-1.549</t>
-  </si>
-  <si>
-    <t>13.31</t>
-  </si>
-  <si>
-    <t>15k</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>-2.25</t>
-  </si>
-  <si>
-    <t>10.75</t>
-  </si>
-  <si>
-    <t>10k</t>
-  </si>
-  <si>
-    <t>0402</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>7.5</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>-29.515</t>
-  </si>
-  <si>
-    <t>16.408</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>8.25</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>9.5</t>
   </si>
   <si>
     <t>R16</t>
@@ -1241,24 +1241,24 @@
         <v>13</v>
       </c>
       <c r="F19" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="H19" s="16" t="s">
         <v>85</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="C20" s="16" t="s">
         <v>88</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>89</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>25</v>
@@ -1270,21 +1270,21 @@
         <v>6</v>
       </c>
       <c r="G20" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>90</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="C21" s="16" t="s">
         <v>93</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>94</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>19</v>
@@ -1296,21 +1296,21 @@
         <v>6</v>
       </c>
       <c r="G21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" s="16" t="s">
         <v>95</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="C22" s="16" t="s">
         <v>98</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>99</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>25</v>
@@ -1322,21 +1322,21 @@
         <v>6</v>
       </c>
       <c r="G22" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="C23" s="16" t="s">
         <v>103</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>104</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>25</v>
@@ -1348,21 +1348,21 @@
         <v>6</v>
       </c>
       <c r="G23" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" s="16" t="s">
         <v>105</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="C24" s="16" t="s">
         <v>108</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>109</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>12</v>
@@ -1374,21 +1374,21 @@
         <v>6</v>
       </c>
       <c r="G24" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="H24" s="16" t="s">
         <v>110</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>77</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D25" s="16" t="s">
         <v>12</v>
@@ -1400,21 +1400,21 @@
         <v>6</v>
       </c>
       <c r="G25" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H25" s="16" t="s">
         <v>114</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="C26" s="16" t="s">
         <v>117</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>118</v>
       </c>
       <c r="D26" s="16" t="s">
         <v>38</v>
@@ -1426,21 +1426,21 @@
         <v>6</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="C27" s="16" t="s">
         <v>121</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>122</v>
       </c>
       <c r="D27" s="16" t="s">
         <v>19</v>
@@ -1452,21 +1452,21 @@
         <v>6</v>
       </c>
       <c r="G27" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H27" s="16" t="s">
         <v>123</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>126</v>
-      </c>
       <c r="C28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>38</v>
@@ -1481,18 +1481,18 @@
         <v>25</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="C29" s="16" t="s">
         <v>128</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>129</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>19</v>
@@ -1504,18 +1504,18 @@
         <v>6</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>132</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>50</v>
@@ -1530,21 +1530,21 @@
         <v>6</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="C31" s="16" t="s">
         <v>135</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>136</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>19</v>
@@ -1553,13 +1553,13 @@
         <v>13</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>12</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1585,7 +1585,7 @@
         <v>140</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1611,7 +1611,7 @@
         <v>144</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1637,7 +1637,7 @@
         <v>147</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:8">
